--- a/Backend/students.xlsx
+++ b/Backend/students.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Ayesha  Malik</t>
+          <t>ayesha Malik</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
